--- a/resultados/Fiscalizacion_Web_DM_guantes-quirurgicos_21-10-2026.xlsx
+++ b/resultados/Fiscalizacion_Web_DM_guantes-quirurgicos_21-10-2026.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Látex, estéril, talla 7.5, venta por par o caja ($600 a $23.300 CLP). La ficha no menciona marca, fabricante ni registro ISP. Imagen no analizada en esta corrida. Tienda en Chile (sucursal Temuco). Verificar envase/imagen.</t>
+          <t>Uso quirúrgico confirmado: la descripción dice uso en ambiente aséptico en procedimientos quirúrgicos (título abrevia QUIR.). Látex, estéril, talla 7.5, venta por par o caja ($600 a $23.300 CLP). La ficha no menciona marca, fabricante ni registro ISP. Imagen no analizada en esta corrida. Tienda en Chile (sucursal Temuco). Verificar envase/imagen.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
